--- a/artfynd/A 40639-2022 artfynd.xlsx
+++ b/artfynd/A 40639-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY170"/>
+  <dimension ref="A1:AY171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18382,6 +18382,117 @@
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>113680527</v>
+      </c>
+      <c r="B171" t="n">
+        <v>90128</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Tallmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>611816</v>
+      </c>
+      <c r="R171" t="n">
+        <v>7036564</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40639-2022 artfynd.xlsx
+++ b/artfynd/A 40639-2022 artfynd.xlsx
@@ -18387,7 +18387,7 @@
         <v>113680527</v>
       </c>
       <c r="B171" t="n">
-        <v>90128</v>
+        <v>90130</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>

--- a/artfynd/A 40639-2022 artfynd.xlsx
+++ b/artfynd/A 40639-2022 artfynd.xlsx
@@ -18387,7 +18387,7 @@
         <v>113680527</v>
       </c>
       <c r="B171" t="n">
-        <v>90130</v>
+        <v>90131</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>

--- a/artfynd/A 40639-2022 artfynd.xlsx
+++ b/artfynd/A 40639-2022 artfynd.xlsx
@@ -18387,7 +18387,7 @@
         <v>113680527</v>
       </c>
       <c r="B171" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>

--- a/artfynd/A 40639-2022 artfynd.xlsx
+++ b/artfynd/A 40639-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40639-2022 artfynd.xlsx
+++ b/artfynd/A 40639-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY184"/>
+  <dimension ref="A1:AZ184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840098</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648302</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840143</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597002</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648308</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648309</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112896081</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648327</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648328</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112896074</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1751,6 +1806,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112896077</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112631075</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1945,6 +2010,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112631076</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2042,6 +2112,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648321</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2143,6 +2218,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112652220</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2244,6 +2324,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112896071</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840111</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840112</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,6 +2630,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840113</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840114</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840115</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2826,6 +2936,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840116</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2923,6 +3038,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840117</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3020,6 +3140,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840118</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3117,6 +3242,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840119</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3214,6 +3344,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607531</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3311,6 +3446,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648305</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3408,6 +3548,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648306</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3514,6 +3659,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680527</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3611,6 +3761,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840173</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3708,6 +3863,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840174</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3805,6 +3965,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597018</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3902,6 +4067,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597019</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3999,6 +4169,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648325</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4096,6 +4271,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648314</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4193,6 +4373,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597021</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4294,6 +4479,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112626698</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4391,6 +4581,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840110</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4488,6 +4683,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840149</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4585,6 +4785,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597009</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4683,6 +4888,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840180</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4780,6 +4990,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840099</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4877,6 +5092,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840100</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4974,6 +5194,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840101</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5071,6 +5296,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840102</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5168,6 +5398,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840103</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5265,6 +5500,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840104</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5362,6 +5602,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840105</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5459,6 +5704,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840106</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5556,6 +5806,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840107</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5653,6 +5908,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112596983</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5750,6 +6010,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112596985</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5847,6 +6112,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112596986</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5944,6 +6214,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112631070</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6041,6 +6316,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112635064</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6138,6 +6418,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648303</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6235,6 +6520,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648304</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6336,6 +6626,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597001</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6433,6 +6728,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112600533</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6530,6 +6830,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840176</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6627,6 +6932,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840177</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6724,6 +7034,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112635068</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6821,6 +7136,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648324</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6918,6 +7238,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648301</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7015,6 +7340,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648312</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7112,6 +7442,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840150</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7209,6 +7544,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840151</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7306,6 +7646,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840152</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7403,6 +7748,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840153</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7500,6 +7850,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840154</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7597,6 +7952,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840155</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7694,6 +8054,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840156</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7791,6 +8156,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840157</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7888,6 +8258,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840158</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7985,6 +8360,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597011</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8082,6 +8462,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597012</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8179,6 +8564,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597013</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8276,6 +8666,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112600524</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8373,6 +8768,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112600526</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8470,6 +8870,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112600527</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8571,6 +8976,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112626699</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8668,6 +9078,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112635066</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8765,6 +9180,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112635067</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8862,6 +9282,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112637648</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8959,6 +9384,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112637649</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9072,6 +9502,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648316</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9169,6 +9604,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648317</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9266,6 +9706,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648318</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9363,6 +9808,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648319</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9460,6 +9910,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648320</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9557,6 +10012,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805893</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9654,6 +10114,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805895</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9751,6 +10216,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805898</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9848,6 +10318,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805900</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9945,6 +10420,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805902</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10042,6 +10522,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597010</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10139,6 +10624,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840139</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10236,6 +10726,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840140</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10333,6 +10828,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840141</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10430,6 +10930,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840142</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10527,6 +11032,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840181</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10629,6 +11139,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840144</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10731,6 +11246,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840145</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10833,6 +11353,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840146</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10938,6 +11463,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648310</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11043,6 +11573,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648311</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11145,6 +11680,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840120</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11247,6 +11787,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840121</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11349,6 +11894,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840122</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11451,6 +12001,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840123</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11553,6 +12108,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840124</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11655,6 +12215,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840125</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11757,6 +12322,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840126</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11859,6 +12429,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840127</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11961,6 +12536,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840128</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12063,6 +12643,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840129</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12165,6 +12750,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840130</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12267,6 +12857,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840131</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12369,6 +12964,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840132</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12471,6 +13071,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840133</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12573,6 +13178,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840134</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12675,6 +13285,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840135</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12777,6 +13392,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112596991</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12879,6 +13499,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112596998</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12981,6 +13606,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597000</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13087,6 +13717,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112600487</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13193,6 +13828,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112600517</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13299,6 +13939,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112600518</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13405,6 +14050,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112600519</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13507,6 +14157,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607538</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13609,6 +14264,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648307</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13711,6 +14371,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648315</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13813,6 +14478,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805849</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13915,6 +14585,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805876</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14017,6 +14692,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805878</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14119,6 +14799,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805881</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14221,6 +14906,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805882</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14323,6 +15013,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805885</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14425,6 +15120,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805887</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14527,6 +15227,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112806972</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14629,6 +15334,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112806974</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14731,6 +15441,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112806999</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14833,6 +15548,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112807001</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14935,6 +15655,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840136</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15063,6 +15788,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112616283</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15191,6 +15921,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112616152</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15288,6 +16023,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840178</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15390,6 +16130,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110890292</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15491,6 +16236,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840161</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15592,6 +16342,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840162</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15693,6 +16448,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840163</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15794,6 +16554,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840164</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15895,6 +16660,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840165</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15996,6 +16766,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840166</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16097,6 +16872,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840167</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16198,6 +16978,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840168</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16299,6 +17084,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840169</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16400,6 +17190,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840170</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16497,6 +17292,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840171</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16598,6 +17398,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840172</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16695,6 +17500,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112600528</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16796,6 +17606,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607539</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16897,6 +17712,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607540</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17013,6 +17833,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112635317</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17119,6 +17944,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112637652</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17220,6 +18050,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648322</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17317,6 +18152,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112648323</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17418,6 +18258,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805904</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17519,6 +18364,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805906</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17620,6 +18470,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805908</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17730,6 +18585,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805910</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17840,6 +18700,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805913</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17950,6 +18815,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112805915</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18051,6 +18921,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112807005</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18152,6 +19027,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112807007</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18253,6 +19133,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112807010</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18354,6 +19239,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112807012</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18455,6 +19345,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112807014</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18556,6 +19451,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112807017</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18653,6 +19553,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597006</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18750,6 +19655,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597005</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18847,6 +19757,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111840182</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18944,8 +19859,198 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112597016</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>